--- a/A2259C_A.xlsx
+++ b/A2259C_A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myrp-my.sharepoint.com/personal/paul_z_chen_rp_edu_sg/Documents/A2259C/A2295C graded assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="11_B662D26A032E6A65B5D124B0443CFCB1B1DB3573" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1D7E664-F7C0-4244-A54B-37FDBF5B8CB9}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_B662D26A032E6A65B5D124B0443CFCB1B1DB3573" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9BAC84E-1055-4285-A617-02E6544309C2}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta" sheetId="8" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="219">
   <si>
     <t>Outlet_ID</t>
   </si>
@@ -731,6 +731,9 @@
 3. biodiverse planting.
 At each site, a biodiversity index score was recorded based on species richness and abundance surveys.
 The study aims to examine whether verge management regime is associated with variation in biodiversity index scores.</t>
+  </si>
+  <si>
+    <t>Briefly discuss one limitation of relying on generative AI to solve this question.</t>
   </si>
 </sst>
 </file>
@@ -797,12 +800,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1135,13 +1139,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E51043-D80A-4957-A953-71F7E375D85F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>212</v>
       </c>
@@ -1149,7 +1153,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="240" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="216" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>211</v>
       </c>
@@ -1157,7 +1161,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="255" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>213</v>
       </c>
@@ -1165,7 +1169,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="300" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="288" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>214</v>
       </c>
@@ -1181,9 +1185,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B70"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1191,7 +1195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1199,7 +1203,7 @@
         <v>15.54</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1207,7 +1211,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1215,7 +1219,7 @@
         <v>11.14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1223,7 +1227,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1231,7 +1235,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1239,7 +1243,7 @@
         <v>10.220000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1247,7 +1251,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1255,7 +1259,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1263,7 +1267,7 @@
         <v>10.11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1271,7 +1275,7 @@
         <v>18.07</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1279,7 +1283,7 @@
         <v>11.17</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1287,7 +1291,7 @@
         <v>11.87</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1295,7 +1299,7 @@
         <v>12.26</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1303,7 +1307,7 @@
         <v>13.94</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1311,7 +1315,7 @@
         <v>14.98</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1319,7 +1323,7 @@
         <v>11.57</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1327,7 +1331,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1335,7 +1339,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1343,7 +1347,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1351,7 +1355,7 @@
         <v>11.22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1359,7 +1363,7 @@
         <v>7.99</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1367,7 +1371,7 @@
         <v>10.26</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -1375,7 +1379,7 @@
         <v>13.35</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1383,7 +1387,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1391,7 +1395,7 @@
         <v>9.4499999999999993</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1399,7 +1403,7 @@
         <v>10.210000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1407,7 +1411,7 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1415,7 +1419,7 @@
         <v>12.93</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1423,7 +1427,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1431,7 +1435,7 @@
         <v>11.17</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1439,7 +1443,7 @@
         <v>10.35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1447,7 +1451,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -1455,7 +1459,7 @@
         <v>11.15</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -1463,7 +1467,7 @@
         <v>16.329999999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -1471,7 +1475,7 @@
         <v>11.31</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -1479,7 +1483,7 @@
         <v>10.33</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -1487,7 +1491,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1495,7 +1499,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -1503,7 +1507,7 @@
         <v>11.02</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -1511,7 +1515,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -1519,7 +1523,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -1527,7 +1531,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -1535,7 +1539,7 @@
         <v>10.56</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -1543,7 +1547,7 @@
         <v>11.54</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -1551,7 +1555,7 @@
         <v>14.33</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -1559,7 +1563,7 @@
         <v>12.96</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -1567,7 +1571,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -1575,7 +1579,7 @@
         <v>8.84</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -1583,7 +1587,7 @@
         <v>11.49</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -1591,7 +1595,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -1599,7 +1603,7 @@
         <v>10.78</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -1607,7 +1611,7 @@
         <v>12.24</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -1615,7 +1619,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -1623,7 +1627,7 @@
         <v>14.68</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1631,7 +1635,7 @@
         <v>9.08</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1639,7 +1643,7 @@
         <v>11.03</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -1647,7 +1651,7 @@
         <v>13.02</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -1655,7 +1659,7 @@
         <v>13.59</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -1663,7 +1667,7 @@
         <v>8.9700000000000006</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -1671,7 +1675,7 @@
         <v>11.03</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -1679,7 +1683,7 @@
         <v>11.91</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -1687,7 +1691,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -1695,7 +1699,7 @@
         <v>8.65</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -1703,7 +1707,7 @@
         <v>10.56</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -1711,7 +1715,7 @@
         <v>10.26</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -1719,7 +1723,7 @@
         <v>15.93</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -1727,7 +1731,7 @@
         <v>12.53</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>67</v>
       </c>
@@ -1735,7 +1739,7 @@
         <v>14.07</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>68</v>
       </c>
@@ -1758,14 +1762,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>180</v>
       </c>
@@ -1776,7 +1780,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1785,7 +1789,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1794,7 +1798,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1803,7 +1807,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1812,7 +1816,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1821,7 +1825,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1830,7 +1834,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1848,7 +1852,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1857,7 +1861,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1878,9 +1882,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>69</v>
       </c>
@@ -1891,7 +1895,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -1902,7 +1906,7 @@
         <v>134.69999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -1913,7 +1917,7 @@
         <v>174.1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1924,7 +1928,7 @@
         <v>205.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -1935,7 +1939,7 @@
         <v>213.9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -1946,7 +1950,7 @@
         <v>290.3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>77</v>
       </c>
@@ -1957,7 +1961,7 @@
         <v>169.6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>78</v>
       </c>
@@ -1968,7 +1972,7 @@
         <v>123.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>79</v>
       </c>
@@ -1979,7 +1983,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>80</v>
       </c>
@@ -1990,7 +1994,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>81</v>
       </c>
@@ -2001,7 +2005,7 @@
         <v>312.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -2012,7 +2016,7 @@
         <v>126.1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>83</v>
       </c>
@@ -2023,7 +2027,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>84</v>
       </c>
@@ -2034,7 +2038,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>85</v>
       </c>
@@ -2045,7 +2049,7 @@
         <v>233.6</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -2056,7 +2060,7 @@
         <v>231.2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -2067,7 +2071,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -2078,7 +2082,7 @@
         <v>176.4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -2089,7 +2093,7 @@
         <v>153.9</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>90</v>
       </c>
@@ -2100,7 +2104,7 @@
         <v>205.6</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>91</v>
       </c>
@@ -2111,7 +2115,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -2122,7 +2126,7 @@
         <v>174.7</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>93</v>
       </c>
@@ -2133,7 +2137,7 @@
         <v>116.7</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>94</v>
       </c>
@@ -2144,7 +2148,7 @@
         <v>157.6</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>95</v>
       </c>
@@ -2155,7 +2159,7 @@
         <v>170.4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>96</v>
       </c>
@@ -2166,7 +2170,7 @@
         <v>166.7</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>97</v>
       </c>
@@ -2177,7 +2181,7 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -2188,7 +2192,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -2199,7 +2203,7 @@
         <v>192.7</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>100</v>
       </c>
@@ -2210,7 +2214,7 @@
         <v>218.7</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>101</v>
       </c>
@@ -2221,7 +2225,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>102</v>
       </c>
@@ -2232,7 +2236,7 @@
         <v>241.1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>103</v>
       </c>
@@ -2243,7 +2247,7 @@
         <v>302.2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>104</v>
       </c>
@@ -2254,7 +2258,7 @@
         <v>164.2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>105</v>
       </c>
@@ -2265,7 +2269,7 @@
         <v>190.3</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>106</v>
       </c>
@@ -2276,7 +2280,7 @@
         <v>178.7</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>107</v>
       </c>
@@ -2287,7 +2291,7 @@
         <v>198.4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>108</v>
       </c>
@@ -2298,7 +2302,7 @@
         <v>149.19999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>109</v>
       </c>
@@ -2309,7 +2313,7 @@
         <v>183.7</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>110</v>
       </c>
@@ -2335,14 +2339,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>180</v>
       </c>
@@ -2353,7 +2357,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2362,7 +2366,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2371,7 +2375,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2380,7 +2384,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2389,7 +2393,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2398,7 +2402,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2407,7 +2411,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2416,7 +2420,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2425,7 +2429,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2434,7 +2438,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2455,9 +2459,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C64"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>111</v>
       </c>
@@ -2468,7 +2472,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -2479,7 +2483,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>116</v>
       </c>
@@ -2490,7 +2494,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>118</v>
       </c>
@@ -2501,7 +2505,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>120</v>
       </c>
@@ -2512,7 +2516,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>121</v>
       </c>
@@ -2523,7 +2527,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>122</v>
       </c>
@@ -2534,7 +2538,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>123</v>
       </c>
@@ -2545,7 +2549,7 @@
         <v>44.8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>124</v>
       </c>
@@ -2556,7 +2560,7 @@
         <v>33.299999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>125</v>
       </c>
@@ -2567,7 +2571,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -2578,7 +2582,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>127</v>
       </c>
@@ -2589,7 +2593,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>128</v>
       </c>
@@ -2600,7 +2604,7 @@
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>129</v>
       </c>
@@ -2611,7 +2615,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>130</v>
       </c>
@@ -2622,7 +2626,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>131</v>
       </c>
@@ -2633,7 +2637,7 @@
         <v>69.139236472733302</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>132</v>
       </c>
@@ -2644,7 +2648,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>133</v>
       </c>
@@ -2655,7 +2659,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>134</v>
       </c>
@@ -2666,7 +2670,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>135</v>
       </c>
@@ -2677,7 +2681,7 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -2688,7 +2692,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>137</v>
       </c>
@@ -2699,7 +2703,7 @@
         <v>41.1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>138</v>
       </c>
@@ -2710,7 +2714,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>139</v>
       </c>
@@ -2721,7 +2725,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>140</v>
       </c>
@@ -2732,7 +2736,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>141</v>
       </c>
@@ -2743,7 +2747,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>142</v>
       </c>
@@ -2754,7 +2758,7 @@
         <v>44.3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -2765,7 +2769,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>144</v>
       </c>
@@ -2776,7 +2780,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>145</v>
       </c>
@@ -2787,7 +2791,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>146</v>
       </c>
@@ -2798,7 +2802,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>147</v>
       </c>
@@ -2809,7 +2813,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>148</v>
       </c>
@@ -2820,7 +2824,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>149</v>
       </c>
@@ -2831,7 +2835,7 @@
         <v>40.9</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>150</v>
       </c>
@@ -2842,7 +2846,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>151</v>
       </c>
@@ -2853,7 +2857,7 @@
         <v>47.1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>152</v>
       </c>
@@ -2864,7 +2868,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>153</v>
       </c>
@@ -2875,7 +2879,7 @@
         <v>33.299999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>154</v>
       </c>
@@ -2886,7 +2890,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>155</v>
       </c>
@@ -2897,7 +2901,7 @@
         <v>31.7</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>156</v>
       </c>
@@ -2908,7 +2912,7 @@
         <v>60.6</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>157</v>
       </c>
@@ -2919,7 +2923,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>158</v>
       </c>
@@ -2930,7 +2934,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>159</v>
       </c>
@@ -2941,7 +2945,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>160</v>
       </c>
@@ -2952,7 +2956,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>161</v>
       </c>
@@ -2963,7 +2967,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>162</v>
       </c>
@@ -2974,7 +2978,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>163</v>
       </c>
@@ -2985,7 +2989,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>164</v>
       </c>
@@ -2996,7 +3000,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>165</v>
       </c>
@@ -3007,7 +3011,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>166</v>
       </c>
@@ -3018,7 +3022,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>167</v>
       </c>
@@ -3029,7 +3033,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>168</v>
       </c>
@@ -3040,7 +3044,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>169</v>
       </c>
@@ -3051,7 +3055,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>170</v>
       </c>
@@ -3062,7 +3066,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>171</v>
       </c>
@@ -3073,7 +3077,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>172</v>
       </c>
@@ -3084,7 +3088,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>173</v>
       </c>
@@ -3095,7 +3099,7 @@
         <v>37.299999999999997</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>174</v>
       </c>
@@ -3106,7 +3110,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>175</v>
       </c>
@@ -3117,7 +3121,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>176</v>
       </c>
@@ -3128,7 +3132,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>177</v>
       </c>
@@ -3139,7 +3143,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>178</v>
       </c>
@@ -3150,7 +3154,7 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>179</v>
       </c>
@@ -3175,15 +3179,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="83.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="83.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>180</v>
       </c>
@@ -3194,7 +3198,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3203,7 +3207,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3212,7 +3216,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3221,7 +3225,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3230,7 +3234,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3239,7 +3243,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3248,7 +3252,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3257,7 +3261,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3266,7 +3270,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3275,7 +3279,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3284,7 +3288,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3292,6 +3296,15 @@
         <v>209</v>
       </c>
       <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
